--- a/docs/perechen-otchetov/obrazcy/ФО-09.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-09.xlsx
@@ -215,16 +215,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,26 +245,23 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
@@ -656,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1003,13 +1003,13 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1</v>
@@ -1041,21 +1041,21 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Действует</t>
+          <t>Зарегистрирован</t>
         </is>
       </c>
       <c r="B9" s="12" t="n"/>
       <c r="C9" s="13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14" t="n"/>
       <c r="H9" s="11" t="n"/>
@@ -1084,13 +1084,13 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>ОсОО «Ак-Дан»</t>
+          <t>ОсОО «Чүй-Тамак»</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
       <c r="C10" s="18" t="n"/>
       <c r="D10" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="19" t="n">
         <v>2</v>
@@ -1122,327 +1122,275 @@
       <c r="AB10" s="18" t="n"/>
       <c r="AC10" s="18" t="n"/>
     </row>
-    <row r="11" ht="13" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>№ 21-3/117 от 15.04.2021</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+          <t>№ 26-3/118 от 20.08.2026</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="25" t="n">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>Заявка № 16 · протокол комиссии № 6 от 06.08.2026</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>48080</v>
+      </c>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="18" t="n"/>
+      <c r="U11" s="18" t="n"/>
+      <c r="V11" s="17" t="n"/>
+      <c r="W11" s="18" t="n"/>
+      <c r="X11" s="17" t="n"/>
+      <c r="Y11" s="18" t="n"/>
+      <c r="Z11" s="20" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="18" t="n"/>
+      <c r="AC11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Транш 1 · 01.09.2026</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>Заявка № 16 · протокол комиссии № 6 от 06.08.2026</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>48080</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L12" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M12" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="O12" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P12" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q12" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S12" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T12" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="25" t="n"/>
+      <c r="W12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y12" s="26" t="n"/>
+      <c r="Z12" s="33" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="26" t="n"/>
+      <c r="AC12" s="26" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Транш 2 · 01.03.2027</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>Заявка № 16 · протокол комиссии № 6 от 06.08.2026</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>48080</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M13" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" s="32" t="n">
+        <v>53</v>
+      </c>
+      <c r="O13" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P13" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q13" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S13" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T13" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="25" t="n"/>
+      <c r="W13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y13" s="26" t="n"/>
+      <c r="Z13" s="33" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="26" t="n"/>
+      <c r="AC13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Действует</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>44301</v>
-      </c>
-      <c r="H11" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>47192</v>
-      </c>
-      <c r="J11" s="28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K11" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L11" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M11" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N11" s="25" t="n">
-        <v>95</v>
-      </c>
-      <c r="O11" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P11" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q11" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="R11" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S11" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T11" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="23" t="n"/>
-      <c r="W11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y11" s="24" t="n"/>
-      <c r="Z11" s="31" t="n"/>
-      <c r="AA11" s="27" t="n"/>
-      <c r="AB11" s="24" t="n"/>
-      <c r="AC11" s="24" t="n"/>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>№ 22-2/031 от 11.03.2022</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="26" t="n">
-        <v>44631</v>
-      </c>
-      <c r="H12" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>46641</v>
-      </c>
-      <c r="J12" s="28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K12" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L12" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M12" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <v>66</v>
-      </c>
-      <c r="O12" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P12" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q12" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="R12" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S12" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T12" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="23" t="n"/>
-      <c r="W12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y12" s="24" t="n"/>
-      <c r="Z12" s="31" t="n"/>
-      <c r="AA12" s="27" t="n"/>
-      <c r="AB12" s="24" t="n"/>
-      <c r="AC12" s="24" t="n"/>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>КФХ «Ак-Суу»</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="18" t="n"/>
-      <c r="K13" s="18" t="n"/>
-      <c r="L13" s="18" t="n"/>
-      <c r="M13" s="18" t="n"/>
-      <c r="N13" s="18" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="18" t="n"/>
-      <c r="U13" s="18" t="n"/>
-      <c r="V13" s="17" t="n"/>
-      <c r="W13" s="18" t="n"/>
-      <c r="X13" s="17" t="n"/>
-      <c r="Y13" s="18" t="n"/>
-      <c r="Z13" s="20" t="n"/>
-      <c r="AA13" s="21" t="n"/>
-      <c r="AB13" s="18" t="n"/>
-      <c r="AC13" s="18" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>№ 20-6/027 от 12.05.2020</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>43963</v>
-      </c>
-      <c r="H14" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>46154</v>
-      </c>
-      <c r="J14" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M14" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N14" s="25" t="n">
-        <v>72</v>
-      </c>
-      <c r="O14" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P14" s="27" t="inlineStr">
-        <is>
-          <t>по месяцам: 5, 11</t>
-        </is>
-      </c>
-      <c r="Q14" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R14" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S14" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T14" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="23" t="n"/>
-      <c r="W14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y14" s="24" t="n"/>
-      <c r="Z14" s="31" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="24" t="n"/>
-      <c r="AC14" s="24" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="11" t="n"/>
+      <c r="P14" s="11" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="11" t="n"/>
+      <c r="S14" s="11" t="n"/>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="12" t="n"/>
+      <c r="W14" s="15" t="n"/>
+      <c r="X14" s="12" t="n"/>
+      <c r="Y14" s="15" t="n"/>
+      <c r="Z14" s="14" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="15" t="n"/>
+      <c r="AC14" s="15" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>ОсОО «Ала-Арча Энерго»</t>
+          <t>ОсОО «Ак-Дан»</t>
         </is>
       </c>
       <c r="B15" s="17" t="n"/>
       <c r="C15" s="18" t="n"/>
       <c r="D15" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>0</v>
@@ -1471,175 +1419,204 @@
       <c r="AB15" s="18" t="n"/>
       <c r="AC15" s="18" t="n"/>
     </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>№ 21-9/040 от 20.09.2021</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="25" t="n">
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>№ 21-3/117 от 15.04.2021</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>44459</v>
-      </c>
-      <c r="H16" s="27" t="inlineStr">
+      <c r="F16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>44301</v>
+      </c>
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>Перенос из старой системы</t>
         </is>
       </c>
-      <c r="I16" s="26" t="n">
-        <v>47016</v>
-      </c>
-      <c r="J16" s="32" t="inlineStr">
-        <is>
-          <t>Euribor-6m + 4,00
-= 6,08</t>
-        </is>
-      </c>
-      <c r="K16" s="32" t="inlineStr">
-        <is>
-          <t>Двукратная учётная ставка НБКР
-= 0,0493</t>
-        </is>
-      </c>
-      <c r="L16" s="32" t="inlineStr">
-        <is>
-          <t>Двукратная учётная ставка НБКР
-= 0,0493</t>
-        </is>
-      </c>
-      <c r="M16" s="30" t="n">
+      <c r="I16" s="27" t="n">
+        <v>47192</v>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L16" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M16" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="N16" s="25" t="n">
-        <v>84</v>
-      </c>
-      <c r="O16" s="27" t="inlineStr">
-        <is>
-          <t>аннуитет</t>
-        </is>
-      </c>
-      <c r="P16" s="27" t="inlineStr">
+      <c r="N16" s="32" t="n">
+        <v>95</v>
+      </c>
+      <c r="O16" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P16" s="28" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="n">
+      <c r="Q16" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="R16" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S16" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T16" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="25" t="n"/>
+      <c r="W16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y16" s="26" t="n"/>
+      <c r="Z16" s="33" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="26" t="n"/>
+      <c r="AC16" s="26" t="n"/>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>№ 22-2/031 от 11.03.2022</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>44631</v>
+      </c>
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>46641</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M17" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="R16" s="27" t="inlineStr">
-        <is>
-          <t>на следующий рабочий день</t>
-        </is>
-      </c>
-      <c r="S16" s="27" t="inlineStr">
+      <c r="N17" s="32" t="n">
+        <v>66</v>
+      </c>
+      <c r="O17" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P17" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q17" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="R17" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S17" s="28" t="inlineStr">
         <is>
           <t>по дате выдачи</t>
         </is>
       </c>
-      <c r="T16" s="25" t="n">
+      <c r="T17" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="U16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="23" t="n"/>
-      <c r="W16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="23" t="inlineStr">
-        <is>
-          <t>факт/360</t>
-        </is>
-      </c>
-      <c r="Y16" s="24" t="n"/>
-      <c r="Z16" s="31" t="n"/>
-      <c r="AA16" s="27" t="n"/>
-      <c r="AB16" s="24" t="n"/>
-      <c r="AC16" s="24" t="n"/>
-    </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>ОсОО «Алтын-Тоо»</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="19" t="n">
+      <c r="U17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="25" t="n"/>
+      <c r="W17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y17" s="26" t="n"/>
+      <c r="Z17" s="33" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="26" t="n"/>
+      <c r="AC17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>КФХ «Ак-Суу»</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="21" t="n"/>
-      <c r="T17" s="18" t="n"/>
-      <c r="U17" s="18" t="n"/>
-      <c r="V17" s="17" t="n"/>
-      <c r="W17" s="18" t="n"/>
-      <c r="X17" s="17" t="n"/>
-      <c r="Y17" s="18" t="n"/>
-      <c r="Z17" s="20" t="n"/>
-      <c r="AA17" s="21" t="n"/>
-      <c r="AB17" s="18" t="n"/>
-      <c r="AC17" s="18" t="n"/>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
-        <is>
-          <t>№ 24-2/088 от 12.03.2024</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
       <c r="E18" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="34" t="n">
-        <v>45363</v>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I18" s="34" t="n">
-        <v>47130</v>
-      </c>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="20" t="n"/>
       <c r="J18" s="18" t="n"/>
       <c r="K18" s="18" t="n"/>
       <c r="L18" s="18" t="n"/>
@@ -1655,340 +1632,311 @@
       <c r="V18" s="17" t="n"/>
       <c r="W18" s="18" t="n"/>
       <c r="X18" s="17" t="n"/>
-      <c r="Y18" s="35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z18" s="34" t="n">
+      <c r="Y18" s="18" t="n"/>
+      <c r="Z18" s="20" t="n"/>
+      <c r="AA18" s="21" t="n"/>
+      <c r="AB18" s="18" t="n"/>
+      <c r="AC18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>№ 20-6/027 от 12.05.2020</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="26" t="n"/>
+      <c r="E19" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>43963</v>
+      </c>
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>46154</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M19" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" s="32" t="n">
+        <v>72</v>
+      </c>
+      <c r="O19" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P19" s="28" t="inlineStr">
+        <is>
+          <t>по месяцам: 5, 11</t>
+        </is>
+      </c>
+      <c r="Q19" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R19" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S19" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T19" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="25" t="n"/>
+      <c r="W19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y19" s="26" t="n"/>
+      <c r="Z19" s="33" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="26" t="n"/>
+      <c r="AC19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Арча Энерго»</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="20" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="21" t="n"/>
+      <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="21" t="n"/>
+      <c r="S20" s="21" t="n"/>
+      <c r="T20" s="18" t="n"/>
+      <c r="U20" s="18" t="n"/>
+      <c r="V20" s="17" t="n"/>
+      <c r="W20" s="18" t="n"/>
+      <c r="X20" s="17" t="n"/>
+      <c r="Y20" s="18" t="n"/>
+      <c r="Z20" s="20" t="n"/>
+      <c r="AA20" s="21" t="n"/>
+      <c r="AB20" s="18" t="n"/>
+      <c r="AC20" s="18" t="n"/>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>№ 21-9/040 от 20.09.2021</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>44459</v>
+      </c>
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>47016</v>
+      </c>
+      <c r="J21" s="35" t="inlineStr">
+        <is>
+          <t>Euribor-6m + 4,00
+= 6,08</t>
+        </is>
+      </c>
+      <c r="K21" s="35" t="inlineStr">
+        <is>
+          <t>Двукратная учётная ставка НБКР
+= 0,0493</t>
+        </is>
+      </c>
+      <c r="L21" s="35" t="inlineStr">
+        <is>
+          <t>Двукратная учётная ставка НБКР
+= 0,0493</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N21" s="32" t="n">
+        <v>84</v>
+      </c>
+      <c r="O21" s="28" t="inlineStr">
+        <is>
+          <t>равными долями с остатком в конце срока</t>
+        </is>
+      </c>
+      <c r="P21" s="28" t="inlineStr">
+        <is>
+          <t>основная сумма — по месяцам: 3; проценты — ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q21" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="R21" s="28" t="inlineStr">
+        <is>
+          <t>на следующий рабочий день</t>
+        </is>
+      </c>
+      <c r="S21" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T21" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="U21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="25" t="n"/>
+      <c r="W21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="25" t="inlineStr">
+        <is>
+          <t>факт/360</t>
+        </is>
+      </c>
+      <c r="Y21" s="26" t="n"/>
+      <c r="Z21" s="33" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="26" t="n"/>
+      <c r="AC21" s="26" t="n"/>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>ОсОО «Алтын-Тоо»</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="20" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="21" t="n"/>
+      <c r="P22" s="21" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="n"/>
+      <c r="T22" s="18" t="n"/>
+      <c r="U22" s="18" t="n"/>
+      <c r="V22" s="17" t="n"/>
+      <c r="W22" s="18" t="n"/>
+      <c r="X22" s="17" t="n"/>
+      <c r="Y22" s="18" t="n"/>
+      <c r="Z22" s="20" t="n"/>
+      <c r="AA22" s="21" t="n"/>
+      <c r="AB22" s="18" t="n"/>
+      <c r="AC22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>№ 24-2/088 от 12.03.2024</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="23" t="n">
         <v>45363</v>
       </c>
-      <c r="AA18" s="21" t="inlineStr">
-        <is>
-          <t>ежеквартально</t>
-        </is>
-      </c>
-      <c r="AB18" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC18" s="36" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>Транш 1 · 20.03.2024</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="26" t="n">
-        <v>45363</v>
-      </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>Перенос из старой системы</t>
         </is>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I23" s="23" t="n">
         <v>47130</v>
       </c>
-      <c r="J19" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M19" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N19" s="25" t="n">
-        <v>58</v>
-      </c>
-      <c r="O19" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P19" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q19" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R19" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S19" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T19" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="23" t="n"/>
-      <c r="W19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y19" s="24" t="n"/>
-      <c r="Z19" s="31" t="n"/>
-      <c r="AA19" s="27" t="n"/>
-      <c r="AB19" s="24" t="n"/>
-      <c r="AC19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Транш 2 · 25.06.2024</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="26" t="n">
-        <v>45363</v>
-      </c>
-      <c r="H20" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I20" s="26" t="n">
-        <v>47130</v>
-      </c>
-      <c r="J20" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M20" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N20" s="25" t="n">
-        <v>55</v>
-      </c>
-      <c r="O20" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P20" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q20" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R20" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S20" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T20" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U20" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="23" t="n"/>
-      <c r="W20" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y20" s="24" t="n"/>
-      <c r="Z20" s="31" t="n"/>
-      <c r="AA20" s="27" t="n"/>
-      <c r="AB20" s="24" t="n"/>
-      <c r="AC20" s="24" t="n"/>
-    </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>ОсОО «Достук Строй»</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="18" t="n"/>
-      <c r="L21" s="18" t="n"/>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="18" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="18" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="n"/>
-      <c r="T21" s="18" t="n"/>
-      <c r="U21" s="18" t="n"/>
-      <c r="V21" s="17" t="n"/>
-      <c r="W21" s="18" t="n"/>
-      <c r="X21" s="17" t="n"/>
-      <c r="Y21" s="18" t="n"/>
-      <c r="Z21" s="20" t="n"/>
-      <c r="AA21" s="21" t="n"/>
-      <c r="AB21" s="18" t="n"/>
-      <c r="AC21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>№ 26-5/090 от 08.09.2026</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>KGS</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="26" t="n">
-        <v>46273</v>
-      </c>
-      <c r="H22" s="27" t="inlineStr">
-        <is>
-          <t>Заявка № 14 · протокол комиссии № 7 от 20.08.2026</t>
-        </is>
-      </c>
-      <c r="I22" s="26" t="n">
-        <v>47376</v>
-      </c>
-      <c r="J22" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L22" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M22" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>36</v>
-      </c>
-      <c r="O22" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P22" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q22" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="R22" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S22" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T22" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U22" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="V22" s="23" t="inlineStr">
-        <is>
-          <t>7–12</t>
-        </is>
-      </c>
-      <c r="W22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y22" s="24" t="n"/>
-      <c r="Z22" s="31" t="n"/>
-      <c r="AA22" s="27" t="n"/>
-      <c r="AB22" s="24" t="n"/>
-      <c r="AC22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>ОсОО «Кара-Балта Мел»</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="20" t="n"/>
       <c r="J23" s="18" t="n"/>
       <c r="K23" s="18" t="n"/>
       <c r="L23" s="18" t="n"/>
@@ -2004,278 +1952,324 @@
       <c r="V23" s="17" t="n"/>
       <c r="W23" s="18" t="n"/>
       <c r="X23" s="17" t="n"/>
-      <c r="Y23" s="18" t="n"/>
-      <c r="Z23" s="20" t="n"/>
-      <c r="AA23" s="21" t="n"/>
-      <c r="AB23" s="18" t="n"/>
-      <c r="AC23" s="18" t="n"/>
+      <c r="Y23" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z23" s="23" t="n">
+        <v>45363</v>
+      </c>
+      <c r="AA23" s="21" t="inlineStr">
+        <is>
+          <t>ежеквартально</t>
+        </is>
+      </c>
+      <c r="AB23" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="37" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>№ 20-2/090 от 12.08.2020</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Транш 1 · 20.03.2024</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="27" t="n">
+        <v>45363</v>
+      </c>
+      <c r="H24" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>47130</v>
+      </c>
+      <c r="J24" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L24" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M24" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="O24" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P24" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q24" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R24" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S24" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T24" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U24" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="25" t="n"/>
+      <c r="W24" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y24" s="26" t="n"/>
+      <c r="Z24" s="33" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="26" t="n"/>
+      <c r="AC24" s="26" t="n"/>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Транш 2 · 25.06.2024</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n">
+        <v>45363</v>
+      </c>
+      <c r="H25" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>47130</v>
+      </c>
+      <c r="J25" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L25" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M25" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="O25" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P25" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q25" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S25" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T25" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="25" t="n"/>
+      <c r="W25" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y25" s="26" t="n"/>
+      <c r="Z25" s="33" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="26" t="n"/>
+      <c r="AC25" s="26" t="n"/>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>ОсОО «Достук Строй»</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="18" t="n"/>
+      <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="18" t="n"/>
+      <c r="U26" s="18" t="n"/>
+      <c r="V26" s="17" t="n"/>
+      <c r="W26" s="18" t="n"/>
+      <c r="X26" s="17" t="n"/>
+      <c r="Y26" s="18" t="n"/>
+      <c r="Z26" s="20" t="n"/>
+      <c r="AA26" s="21" t="n"/>
+      <c r="AB26" s="18" t="n"/>
+      <c r="AC26" s="18" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>№ 26-5/090 от 08.09.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="25" t="n">
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="26" t="n">
+      <c r="F27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27" t="n">
         <v>46273</v>
       </c>
-      <c r="H24" s="27" t="inlineStr">
-        <is>
-          <t>Доп. соглашение № 2 от 08.09.2026</t>
-        </is>
-      </c>
-      <c r="I24" s="26" t="n">
-        <v>47342</v>
-      </c>
-      <c r="J24" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K24" s="29" t="n">
+      <c r="H27" s="28" t="inlineStr">
+        <is>
+          <t>Заявка № 14 · протокол комиссии № 7 от 20.08.2026</t>
+        </is>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>47376</v>
+      </c>
+      <c r="J27" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="L24" s="29" t="n">
+      <c r="L27" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="M24" s="30" t="n">
+      <c r="M27" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="N24" s="39" t="n">
-        <v>108</v>
-      </c>
-      <c r="O24" s="27" t="inlineStr">
+      <c r="N27" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="O27" s="28" t="inlineStr">
         <is>
           <t>равными долями</t>
         </is>
       </c>
-      <c r="P24" s="27" t="inlineStr">
+      <c r="P27" s="28" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="Q24" s="25" t="n">
+      <c r="Q27" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="R27" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S27" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T27" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="R24" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S24" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T24" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="U24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="23" t="n"/>
-      <c r="W24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="23" t="inlineStr">
+      <c r="U27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" s="25" t="inlineStr">
+        <is>
+          <t>7–12</t>
+        </is>
+      </c>
+      <c r="W27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="25" t="inlineStr">
         <is>
           <t>факт/факт</t>
         </is>
       </c>
-      <c r="Y24" s="24" t="n"/>
-      <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="27" t="n"/>
-      <c r="AB24" s="24" t="n"/>
-      <c r="AC24" s="24" t="n"/>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>ОсОО «Кут-Мүлк»</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="21" t="n"/>
-      <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="18" t="n"/>
-      <c r="R25" s="21" t="n"/>
-      <c r="S25" s="21" t="n"/>
-      <c r="T25" s="18" t="n"/>
-      <c r="U25" s="18" t="n"/>
-      <c r="V25" s="17" t="n"/>
-      <c r="W25" s="18" t="n"/>
-      <c r="X25" s="17" t="n"/>
-      <c r="Y25" s="18" t="n"/>
-      <c r="Z25" s="20" t="n"/>
-      <c r="AA25" s="21" t="n"/>
-      <c r="AB25" s="18" t="n"/>
-      <c r="AC25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>№ 23-1/019 от 05.05.2023</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="26" t="n">
-        <v>45051</v>
-      </c>
-      <c r="H26" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I26" s="26" t="n">
-        <v>46604</v>
-      </c>
-      <c r="J26" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K26" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L26" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M26" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N26" s="25" t="n">
-        <v>51</v>
-      </c>
-      <c r="O26" s="27" t="inlineStr">
-        <is>
-          <t>равными долями</t>
-        </is>
-      </c>
-      <c r="P26" s="27" t="inlineStr">
-        <is>
-          <t>ежемесячно</t>
-        </is>
-      </c>
-      <c r="Q26" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R26" s="27" t="inlineStr">
-        <is>
-          <t>не переносить</t>
-        </is>
-      </c>
-      <c r="S26" s="27" t="inlineStr">
-        <is>
-          <t>по дате выдачи</t>
-        </is>
-      </c>
-      <c r="T26" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="U26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="23" t="n"/>
-      <c r="W26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="23" t="inlineStr">
-        <is>
-          <t>факт/факт</t>
-        </is>
-      </c>
-      <c r="Y26" s="24" t="n"/>
-      <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="27" t="n"/>
-      <c r="AB26" s="24" t="n"/>
-      <c r="AC26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Закрыт</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="14" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
-      <c r="M27" s="15" t="n"/>
-      <c r="N27" s="15" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="15" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="15" t="n"/>
-      <c r="U27" s="15" t="n"/>
-      <c r="V27" s="12" t="n"/>
-      <c r="W27" s="15" t="n"/>
-      <c r="X27" s="12" t="n"/>
-      <c r="Y27" s="15" t="n"/>
-      <c r="Z27" s="14" t="n"/>
-      <c r="AA27" s="11" t="n"/>
-      <c r="AB27" s="15" t="n"/>
-      <c r="AC27" s="15" t="n"/>
+      <c r="Y27" s="26" t="n"/>
+      <c r="Z27" s="33" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="26" t="n"/>
+      <c r="AC27" s="26" t="n"/>
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>ОсОО «Ош-Нан»</t>
+          <t>ОсОО «Кара-Балта Мел»</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -2287,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="21" t="n"/>
@@ -2314,98 +2308,98 @@
       <c r="AC28" s="18" t="n"/>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>№ 20-1/412 от 14.10.2020</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>№ 20-2/090 от 12.08.2020</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="25" t="n">
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>44118</v>
-      </c>
-      <c r="H29" s="27" t="inlineStr">
-        <is>
-          <t>Перенос из старой системы</t>
-        </is>
-      </c>
-      <c r="I29" s="26" t="n">
-        <v>46674</v>
-      </c>
-      <c r="J29" s="28" t="n">
+      <c r="F29" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H29" s="28" t="inlineStr">
+        <is>
+          <t>Доп. соглашение № 2 от 08.09.2026</t>
+        </is>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>47342</v>
+      </c>
+      <c r="J29" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="29" t="n">
+      <c r="K29" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="L29" s="29" t="n">
+      <c r="L29" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="M29" s="30" t="n">
+      <c r="M29" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="N29" s="25" t="n">
-        <v>84</v>
-      </c>
-      <c r="O29" s="27" t="inlineStr">
+      <c r="N29" s="39" t="n">
+        <v>108</v>
+      </c>
+      <c r="O29" s="28" t="inlineStr">
         <is>
           <t>равными долями</t>
         </is>
       </c>
-      <c r="P29" s="27" t="inlineStr">
+      <c r="P29" s="28" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="Q29" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="R29" s="27" t="inlineStr">
+      <c r="Q29" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="R29" s="28" t="inlineStr">
         <is>
           <t>не переносить</t>
         </is>
       </c>
-      <c r="S29" s="27" t="inlineStr">
+      <c r="S29" s="28" t="inlineStr">
         <is>
           <t>по дате выдачи</t>
         </is>
       </c>
-      <c r="T29" s="25" t="n">
+      <c r="T29" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="U29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="23" t="n"/>
-      <c r="W29" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="23" t="inlineStr">
+      <c r="U29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="25" t="n"/>
+      <c r="W29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="25" t="inlineStr">
         <is>
           <t>факт/факт</t>
         </is>
       </c>
-      <c r="Y29" s="24" t="n"/>
-      <c r="Z29" s="31" t="n"/>
-      <c r="AA29" s="27" t="n"/>
-      <c r="AB29" s="24" t="n"/>
-      <c r="AC29" s="24" t="n"/>
+      <c r="Y29" s="26" t="n"/>
+      <c r="Z29" s="33" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="26" t="n"/>
+      <c r="AC29" s="26" t="n"/>
     </row>
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>ОсОО «Тянь-Шань Металл»</t>
+          <t>ОсОО «Кут-Мүлк»</t>
         </is>
       </c>
       <c r="B30" s="17" t="n"/>
@@ -2444,93 +2438,396 @@
       <c r="AC30" s="18" t="n"/>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>№ 23-1/019 от 05.05.2023</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>45051</v>
+      </c>
+      <c r="H31" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>46604</v>
+      </c>
+      <c r="J31" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L31" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M31" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N31" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="O31" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P31" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q31" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R31" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S31" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T31" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="25" t="n"/>
+      <c r="W31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y31" s="26" t="n"/>
+      <c r="Z31" s="33" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="26" t="n"/>
+      <c r="AC31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Закрыт</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="11" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="11" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="15" t="n"/>
+      <c r="U32" s="15" t="n"/>
+      <c r="V32" s="12" t="n"/>
+      <c r="W32" s="15" t="n"/>
+      <c r="X32" s="12" t="n"/>
+      <c r="Y32" s="15" t="n"/>
+      <c r="Z32" s="14" t="n"/>
+      <c r="AA32" s="11" t="n"/>
+      <c r="AB32" s="15" t="n"/>
+      <c r="AC32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Нан»</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="21" t="n"/>
+      <c r="P33" s="21" t="n"/>
+      <c r="Q33" s="18" t="n"/>
+      <c r="R33" s="21" t="n"/>
+      <c r="S33" s="21" t="n"/>
+      <c r="T33" s="18" t="n"/>
+      <c r="U33" s="18" t="n"/>
+      <c r="V33" s="17" t="n"/>
+      <c r="W33" s="18" t="n"/>
+      <c r="X33" s="17" t="n"/>
+      <c r="Y33" s="18" t="n"/>
+      <c r="Z33" s="20" t="n"/>
+      <c r="AA33" s="21" t="n"/>
+      <c r="AB33" s="18" t="n"/>
+      <c r="AC33" s="18" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>№ 20-1/412 от 14.10.2020</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>44118</v>
+      </c>
+      <c r="H34" s="28" t="inlineStr">
+        <is>
+          <t>Перенос из старой системы</t>
+        </is>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>46674</v>
+      </c>
+      <c r="J34" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L34" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M34" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N34" s="32" t="n">
+        <v>84</v>
+      </c>
+      <c r="O34" s="28" t="inlineStr">
+        <is>
+          <t>равными долями</t>
+        </is>
+      </c>
+      <c r="P34" s="28" t="inlineStr">
+        <is>
+          <t>ежемесячно</t>
+        </is>
+      </c>
+      <c r="Q34" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="R34" s="28" t="inlineStr">
+        <is>
+          <t>не переносить</t>
+        </is>
+      </c>
+      <c r="S34" s="28" t="inlineStr">
+        <is>
+          <t>по дате выдачи</t>
+        </is>
+      </c>
+      <c r="T34" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="25" t="n"/>
+      <c r="W34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="25" t="inlineStr">
+        <is>
+          <t>факт/факт</t>
+        </is>
+      </c>
+      <c r="Y34" s="26" t="n"/>
+      <c r="Z34" s="33" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="26" t="n"/>
+      <c r="AC34" s="26" t="n"/>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Металл»</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="21" t="n"/>
+      <c r="P35" s="21" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="21" t="n"/>
+      <c r="S35" s="21" t="n"/>
+      <c r="T35" s="18" t="n"/>
+      <c r="U35" s="18" t="n"/>
+      <c r="V35" s="17" t="n"/>
+      <c r="W35" s="18" t="n"/>
+      <c r="X35" s="17" t="n"/>
+      <c r="Y35" s="18" t="n"/>
+      <c r="Z35" s="20" t="n"/>
+      <c r="AA35" s="21" t="n"/>
+      <c r="AB35" s="18" t="n"/>
+      <c r="AC35" s="18" t="n"/>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>№ 20-3/052 от 21.07.2020</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>KGS</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="25" t="n">
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="26" t="n">
+      <c r="F36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="27" t="n">
         <v>44033</v>
       </c>
-      <c r="H31" s="27" t="inlineStr">
+      <c r="H36" s="28" t="inlineStr">
         <is>
           <t>Перенос из старой системы</t>
         </is>
       </c>
-      <c r="I31" s="26" t="n">
+      <c r="I36" s="27" t="n">
         <v>46589</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J36" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="29" t="n">
+      <c r="K36" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="L31" s="29" t="n">
+      <c r="L36" s="30" t="n">
         <v>0.05</v>
       </c>
-      <c r="M31" s="30" t="n">
+      <c r="M36" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="N31" s="25" t="n">
+      <c r="N36" s="32" t="n">
         <v>84</v>
       </c>
-      <c r="O31" s="27" t="inlineStr">
+      <c r="O36" s="28" t="inlineStr">
         <is>
           <t>равными долями</t>
         </is>
       </c>
-      <c r="P31" s="27" t="inlineStr">
+      <c r="P36" s="28" t="inlineStr">
         <is>
           <t>ежемесячно</t>
         </is>
       </c>
-      <c r="Q31" s="25" t="n">
+      <c r="Q36" s="32" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="27" t="inlineStr">
+      <c r="R36" s="28" t="inlineStr">
         <is>
           <t>не переносить</t>
         </is>
       </c>
-      <c r="S31" s="27" t="inlineStr">
+      <c r="S36" s="28" t="inlineStr">
         <is>
           <t>по дате выдачи</t>
         </is>
       </c>
-      <c r="T31" s="25" t="n">
+      <c r="T36" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="U31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="23" t="n"/>
-      <c r="W31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="23" t="inlineStr">
+      <c r="U36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="25" t="n"/>
+      <c r="W36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="25" t="inlineStr">
         <is>
           <t>факт/факт</t>
         </is>
       </c>
-      <c r="Y31" s="24" t="n"/>
-      <c r="Z31" s="31" t="n"/>
-      <c r="AA31" s="27" t="n"/>
-      <c r="AB31" s="24" t="n"/>
-      <c r="AC31" s="24" t="n"/>
+      <c r="Y36" s="26" t="n"/>
+      <c r="Z36" s="33" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="26" t="n"/>
+      <c r="AC36" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2862,7 +3159,7 @@
       <c r="H10" s="21" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>№ 20-2/090 от 12.08.2020</t>
         </is>
@@ -2889,12 +3186,12 @@
       <c r="C12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="23" t="n">
         <v>46273</v>
       </c>
       <c r="E12" s="21" t="n"/>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="34" t="n">
+      <c r="G12" s="23" t="n">
         <v>46273</v>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -2909,21 +3206,21 @@
           <t>Ставка, % годовых</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>12,50</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>10,00</t>
         </is>
       </c>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="G13" s="33" t="n"/>
+      <c r="H13" s="28" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
@@ -2931,21 +3228,21 @@
           <t>Срок, мес.</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="31" t="n"/>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="G14" s="31" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="G14" s="33" t="n"/>
+      <c r="H14" s="28" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
@@ -2953,21 +3250,21 @@
           <t>Льгота по основной сумме, мес.</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F15" s="27" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="27" t="n"/>
+      <c r="G15" s="33" t="n"/>
+      <c r="H15" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3123,7 +3420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3571,7 +3868,7 @@
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
-          <t>аннуитет, равными долями, в конце срока</t>
+          <t>аннуитет, равными долями, равными долями с остатком в конце срока, в конце срока</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3885,7 @@
       </c>
       <c r="C37" s="47" t="inlineStr">
         <is>
-          <t>ежемесячно, ежеквартально, раз в полгода, ежегодно; по конкретным месяцам — с номерами месяцев: «по месяцам: 5, 11»</t>
+          <t>ежемесячно, ежеквартально, раз в полгода, ежегодно; по конкретным месяцам — с номерами месяцев: «по месяцам: 5, 11»; если основная сумма и проценты платятся с разной периодичностью — обе: «основная сумма — по месяцам: 3; проценты — ежемесячно»</t>
         </is>
       </c>
     </row>
@@ -3820,7 +4117,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53" ht="90" customHeight="1">
       <c r="A53" s="46" t="inlineStr">
         <is>
           <t>1.</t>
@@ -3828,7 +4125,7 @@
       </c>
       <c r="B53" s="47" t="inlineStr">
         <is>
-          <t>На 01.10.2026 по всему набору: 25 заёмщиков, 28 кредитов — действует 24, закрыт 4 (КЗ-08 списан, КЗ-15 погашен, КЗ-16 погашен имуществом, КЗ-18 расторгнут); проектов и зарегистрированных нет. Кредитов в состоянии «Действует» столько же, сколько в ФО-02 на 01.10.2026 (24). Образец — выборка из 9 заёмщиков: ИТОГО 9 заёмщиков, 10 кредитов, 11 траншей, 1 изменение.</t>
+          <t>На 01.10.2026 по всему набору: 26 заёмщиков, 29 кредитов — зарегистрирован 1 (КЗ-26), действует 24, закрыт 4 (КЗ-08 списан, КЗ-15 погашен, КЗ-16 погашен имуществом, КЗ-18 расторгнут); проектов нет. КЗ-07 — под ОсОО «Ысык-Көл Логистик», заёмщиком на дату (долг переведён 09.09.2026), строки ОсОО «Эко-Продукт» нет. По состояниям — как сверка ФО-58 на 30.09.2026: «Действует» 24 (= кредитов в ФО-02 и ФО-28), «Зарегистрирован» 1 (= ФО-08), «Закрыт» 4. Образец — выборка из 10 заёмщиков: ИТОГО 10 заёмщиков, 11 кредитов, 13 траншей, 1 изменение.</t>
         </is>
       </c>
     </row>
@@ -3856,7 +4153,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="165" customHeight="1">
       <c r="A56" s="46" t="inlineStr">
         <is>
           <t>4.</t>
@@ -3864,7 +4161,7 @@
       </c>
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>КЗ-25 № 21-9/040 (EUR, плавающие ставки): ставка «Euribor-6m + 4,00 = 6,08» — Euribor-6m на 30.09.2026 2,08; штрафы «Двукратная учётная ставка НБКР = 0,0493» — 2 × 9,00 % / 365; выделения нет: тип и маржа не менялись, ежедневный пересчёт — не изменение; метод погашения — аннуитет, метод дней факт/360, нерабочие дни — на следующий рабочий день.</t>
+          <t>КЗ-25 № 21-9/040 (EUR, плавающие ставки): ставка «Euribor-6m + 4,00 = 6,08» — Euribor-6m на 30.09.2026 2,08; штрафы «Двукратная учётная ставка НБКР = 0,0493» — 2 × 9,00 % / 365; выделения нет: тип и маржа не менялись, ежедневный пересчёт — не изменение; метод дней факт/360, платёж 20-го числа, нерабочие дни — на следующий рабочий день. Погашение — по графику набора (на подтверждение): проценты ежемесячно, основная сумма 20 марта ежегодно по 12 000,00 EUR с 2023 года, остаток 48 000,00 EUR — в срок возврата 20.09.2028; отсюда метод «равными долями с остатком в конце срока», периодичность «основная сумма — по месяцам: 3; проценты — ежемесячно», льгота по основной сумме 18 мес. (20.09.2021 → первый платёж 20.03.2023); 120 000,00 − 4 × 12 000,00 = остаток 72 000,00 EUR (= ФО-02), ещё 2 × 12 000,00 + 48 000,00 до срока. Аннуитет, стоявший здесь раньше, с графиком не сходился. В реестре условий транша (ТЗ 05) одна периодичность и три метода — такой график им не задаётся (на подтверждение).</t>
         </is>
       </c>
     </row>
@@ -3880,7 +4177,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="150" customHeight="1">
       <c r="A58" s="46" t="inlineStr">
         <is>
           <t>6.</t>
@@ -3888,11 +4185,11 @@
       </c>
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>КЗ-17 № 26-5/090 — кредит, выданный через заявку новой системы: основание «Заявка № 14 · протокол комиссии № 7 от 20.08.2026», условия с 08.09.2026, срок 36 мес., возврат 15.09.2029; льгота по процентам 6 мес., отсроченные проценты распределены на периоды 7–12. У остальных кредитов выборки первичные условия перенесены из старой системы — основание «Перенос из старой системы».</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
+          <t>КЗ-17 № 26-5/090 — кредит, выданный через заявку новой системы: основание «Заявка № 14 · протокол комиссии № 7 от 20.08.2026», условия с 08.09.2026 (дата договора; в «Действует» 15.09.2026 — смена состояния, не изменение условий), срок 36 мес., возврат 15.09.2029; льгота по процентам 6 мес., отсроченные проценты распределены на периоды 7–12. КЗ-26 № 26-3/118 — «Зарегистрирован», освоений нет (= ФО-08): условия показаны, как у действующего, — основание «Заявка № 16 · протокол комиссии № 6 от 06.08.2026», условия с 20.08.2026, ставка 6 %, возврат 20.08.2031; два транша по плановым датам выдачи (01.09.2026 — 59 мес., 01.03.2027 — 53 мес.); плата за неосвоенный остаток договором не установлена — пять колонок платы пусты (в отличие от КЗ-12). У остальных кредитов выборки первичные условия перенесены из старой системы — основание «Перенос из старой системы».</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="46" t="inlineStr">
         <is>
           <t>7.</t>
@@ -3900,7 +4197,7 @@
       </c>
       <c r="B59" s="47" t="inlineStr">
         <is>
-          <t>КЗ-24 № 20-6/027 (кредит АПК): платежи по конкретным месяцам — «по месяцам: 5, 11»; срок возврата 12.05.2026 прошёл, кредит «Действует» — остались неоплаченные штрафы. КЗ-08 и КЗ-15 — «Закрыт», условия на дату закрытия (17.09.2026 и 18.09.2026).</t>
+          <t>КЗ-24 № 20-6/027 (кредит АПК): платежи по конкретным месяцам — «по месяцам: 5, 11»; срок возврата 12.05.2026 прошёл, кредит «Действует» — остались неоплаченные штрафы. КЗ-08 и КЗ-15 — «Закрыт», условия на дату закрытия (17.09.2026 и 18.09.2026); так же в полном отчёте КЗ-16 (20.03.2026) и КЗ-18 (расторгнут 10.09.2026 из «Зарегистрирован»).</t>
         </is>
       </c>
     </row>
@@ -3928,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="105" customHeight="1">
+    <row r="62" ht="120" customHeight="1">
       <c r="A62" s="46" t="inlineStr">
         <is>
           <t>10.</t>
@@ -3936,48 +4233,60 @@
       </c>
       <c r="B62" s="47" t="inlineStr">
         <is>
-          <t>Условия, не заданные в наборе (кроме КЗ-25), в образце: штрафы 0,05 % в день, предел штрафов 20 % суммы кредита, метод погашения — равными долями, ежемесячно, день платежа — число даты договора, нерабочие дни — не переносить, последний платёж — по дате выдачи, льгота по основной сумме 12 мес. (у КЗ-06 до соглашения — 6), по процентам и отсрочка — 0 (у КЗ-17 по процентам — 6), метод дней факт/факт; срок КЗ-06 до соглашения — 84 мес.; сроки возврата КЗ-08 — 21.07.2027, КЗ-15 — 14.10.2027; ставки КЗ-12 — 8 %, КЗ-11 — 6 %, КЗ-08 и КЗ-15 — 10 % (восстановлены из начислений ФО-07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="48" t="inlineStr">
+          <t>Условия, не заданные в наборе (кроме КЗ-25 — по его графику), в образце: штрафы 0,05 % в день, предел штрафов 20 % суммы кредита, метод погашения — равными долями, ежемесячно, день платежа — число даты договора (у КЗ-17 — даты выдачи, 15), нерабочие дни — не переносить, последний платёж — по дате выдачи, льгота по основной сумме 12 мес. (у КЗ-06 до соглашения — 6), по процентам и отсрочка — 0 (у КЗ-17 по процентам — 6), метод дней факт/факт; срок КЗ-06 до соглашения — 84 мес.; сроки возврата КЗ-08 — 21.07.2027, КЗ-15 — 14.10.2027; ставки КЗ-12 — 8 %, КЗ-11 — 6 %, КЗ-08 и КЗ-15 — 10 % (восстановлены из начислений ФО-07); сроки траншей КЗ-26 — от плановой даты выдачи до срока возврата.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="46" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B63" s="47" t="inlineStr">
+        <is>
+          <t>КЗ-11 № 23-1/019: ставка 6 %, факт/факт — по цепочке начислений набора (ФО-07, ФО-02): начислено за сентябрь 0,27535 тыс. USD = 5 дней на 60 000,00 и 25 дней на 55 000,00 по 6 %/365, уплачено 05.09.2026 275,00 USD — начисленное к этой дате 275,47 USD (остаток 0,47 USD входит в 226,50 на 30.09.2026). Прочтение «275,00 = 60 000,00 × 5,5 % / 12, 30/360» сходится только с сентябрём: в плане ФО-06 проценты КЗ-11 каждого месяца = остаток после платежа × 6 % / 12 (январь 475,00 USD = 95 000,00 × 0,5 %), при 5,5 % январь дал бы 458,33. Источник — 6 % (на подтверждение).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="inlineStr">
         <is>
           <t>Вид 1: «Изменения условий кредитов за период» — лист «Вид 1»</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="75" customHeight="1">
-      <c r="A65" s="46" t="inlineStr">
+    <row r="66" ht="75" customHeight="1">
+      <c r="A66" s="46" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B65" s="47" t="inlineStr">
+      <c r="B66" s="47" t="inlineStr">
         <is>
           <t>Бухгалтерии и кураторам — какими документами за период изменены условия кредитов: документ, дата вступления, какие условия и как (было → стало), когда и кем внесено. Объясняет, почему график и начисление (ФО-07) разошлись с прежним расчётом, в том числе после изменения, внесённого задним числом. Действующие условия на дату — основной отчёт; факт изменения состояния кредита без подробностей — ФО-58.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="46" t="inlineStr">
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="46" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B66" s="47" t="inlineStr">
+      <c r="B67" s="47" t="inlineStr">
         <is>
           <t>За период: по требованию и после закрытия месяца; по умолчанию — прошлый месяц. Можно выбрать любой период.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="120" customHeight="1">
-      <c r="A67" s="46" t="inlineStr">
+    <row r="68" ht="120" customHeight="1">
+      <c r="A68" s="46" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B67" s="47" t="inlineStr">
+      <c r="B68" s="47" t="inlineStr">
         <is>
           <t>• Период — прошлый месяц; можно выбрать любой
 • Разрезы — до шести уровней в любом порядке; по умолчанию состояние → заёмщик → кредит → документ → условие. Доступны: состояние, департамент, отдел, куратор, валюта, кредитная программа, вид кредита, источник финансирования, кредитная линия, область, район, ставка, тип плавающей ставки, заёмщик
@@ -3985,128 +4294,128 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="225" customHeight="1">
-      <c r="A68" s="46" t="inlineStr">
+    <row r="69" ht="225" customHeight="1">
+      <c r="A69" s="46" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B68" s="47" t="inlineStr">
+      <c r="B69" s="47" t="inlineStr">
         <is>
           <t>Под кредитом — строка документа, которым изменены условия: «Доп. соглашение № 2 от 08.09.2026», решение суда, постановление Правительства; под ней — строки изменённых условий (строка детали) с названием условия, как колонка основного отчёта, и значениями «было» и «стало». Как «История изменений» на вкладке «Условия» карточки кредита. Строка документа несёт число изменённых условий, дату вступления, дату внесения и кто внёс. У кредита с несколькими траншами, если документ изменил транши по-разному, между документом и условием — строка транша; изменение условий платы за неосвоенный остаток — без строки транша. Изменение попадает, если в периоде его дата вступления или дата внесения: внесённое задним числом показывается и в месяце вступления, и в месяце внесения. Первичные условия из заявки и решения комиссии при регистрации кредита или нового транша — не изменение и не показываются. Ежедневный пересчёт плавающей ставки или штрафа по значению их типа — тоже не изменение; изменение — смена типа или маржи. Над кредитами разрезы, по умолчанию состояние → заёмщик; строка разреза несёт число документов и изменённых условий. Первая строка — ИТОГО. Порядок: состояния, заёмщики, кредиты — как в основном отчёте; документы кредита — по дате вступления; условия документа — в порядке колонок основного отчёта. Сумм нет — без единицы в заголовке.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="46" t="inlineStr">
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="46" t="inlineStr">
         <is>
           <t>Разрезы</t>
         </is>
       </c>
-      <c r="B69" s="47" t="inlineStr">
+      <c r="B70" s="47" t="inlineStr">
         <is>
           <t>по умолчанию: Состояние → Заёмщик → Кредит → документ → условие; можно выбрать: Состояние, Департамент, Отдел, Куратор, Валюта, Кредитная программа, Вид кредита, Источник финансирования, Кредитная линия, Область, Район, Ставка, Тип плавающей ставки, Заёмщик</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="46" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="B70" s="47" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶419–427; ТЗ 05</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="46" t="inlineStr">
         <is>
-          <t>Образец-основа</t>
+          <t>Основание</t>
         </is>
       </c>
       <c r="B71" s="47" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>оф. ТЗ ¶419–427; ТЗ 05</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="46" t="inlineStr">
         <is>
+          <t>Образец-основа</t>
+        </is>
+      </c>
+      <c r="B72" s="47" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="46" t="inlineStr">
+        <is>
           <t>Колонки</t>
         </is>
       </c>
-      <c r="B72" s="47" t="inlineStr">
+      <c r="B73" s="47" t="inlineStr">
         <is>
           <t>Наименование; Изменений; Условий; Вступило; Было; Стало; Внесено; Кем внесено</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="75" customHeight="1">
-      <c r="A73" s="46" t="inlineStr">
+    <row r="74" ht="75" customHeight="1">
+      <c r="A74" s="46" t="inlineStr">
         <is>
           <t>Проверка 1</t>
         </is>
       </c>
-      <c r="B73" s="47" t="inlineStr">
+      <c r="B74" s="47" t="inlineStr">
         <is>
           <t>Сентябрь 2026: одно изменение у одного кредита — КЗ-06 № 20-2/090, доп. соглашение № 2 от 08.09.2026, три условия: ставка 12,50 → 10,00, срок 84 → 108 мес., льгота по основной сумме 6 → 12 мес. В основном отчёте на 01.10.2026 у КЗ-06 «Изменений» 1 и эти три ячейки выделены; в ФО-58 за тот же период у КЗ-06 одно событие «Изменение условий (реструктуризация)» с тем же основанием; в ФО-10 (вид «Влияние реструктуризации») — та же ставка и тот же срок до и после.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="45" customHeight="1">
-      <c r="A74" s="46" t="inlineStr">
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="46" t="inlineStr">
         <is>
           <t>Проверка 2</t>
         </is>
       </c>
-      <c r="B74" s="47" t="inlineStr">
-        <is>
-          <t>Не показываются: регистрация КЗ-17 (08.09.2026) — первичные условия из заявки — не изменение; перевод долга КЗ-07 (09.09.2026) и соглашение о добровольном исполнении КЗ-05 (10.09.2026) условия не меняют.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="46" t="inlineStr">
-        <is>
-          <t>Проверка 3</t>
-        </is>
-      </c>
       <c r="B75" s="47" t="inlineStr">
         <is>
-          <t>Изменение, внесённое в периоде задним числом (вступило раньше начала периода), показывается; изменение, вступившее в периоде и внесённое позже, показывается при формировании после внесения.</t>
+          <t>Не показываются: регистрация КЗ-17 (08.09.2026) — первичные условия из заявки — не изменение; вступление КЗ-17 в действие 15.09.2026, расторжение КЗ-18 10.09.2026, списание КЗ-08 17.09.2026 и погашение КЗ-15 18.09.2026 — смена состояния (ФО-58), не условий; перевод долга КЗ-07 (09.09.2026, соглашение № 14) меняет заёмщика, не условия — в ФО-58 «Перевод долга»; соглашение о добровольном исполнении КЗ-05 (10.09.2026) условия не меняет; КЗ-26 — зарегистрирован 20.08.2026, в сентябре изменений нет.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="46" t="inlineStr">
         <is>
+          <t>Проверка 3</t>
+        </is>
+      </c>
+      <c r="B76" s="47" t="inlineStr">
+        <is>
+          <t>Изменение, внесённое в периоде задним числом (вступило раньше начала периода), показывается; изменение, вступившее в периоде и внесённое позже, показывается при формировании после внесения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="46" t="inlineStr">
+        <is>
           <t>Проверка 4</t>
         </is>
       </c>
-      <c r="B76" s="47" t="inlineStr">
-        <is>
-          <t>КЗ-25 (Euribor-6m + 4,00, пересчёт ежедневно) в сентябре не показывается: тип и маржа не менялись, ежедневные значения ставки — не изменения условий.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="46" t="inlineStr">
+      <c r="B77" s="47" t="inlineStr">
+        <is>
+          <t>КЗ-25 (Euribor-6m + 4,00, пересчёт ежедневно; Euribor-6m с 21.08.2026 — 2,08, ставка 6,08 %) в сентябре не показывается: тип и маржа не менялись, ежедневные значения ставки — не изменения условий.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="46" t="inlineStr">
         <is>
           <t>Проверка 5</t>
         </is>
       </c>
-      <c r="B77" s="47" t="inlineStr">
+      <c r="B78" s="47" t="inlineStr">
         <is>
           <t>Подытоги и ИТОГО: «Изменений» — число строк-документов ниже, «Условий» — число строк-условий ниже.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="B62:C62"/>
@@ -4134,9 +4443,9 @@
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B78:C78"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B65:C65"/>
     <mergeCell ref="B74:C74"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="B6:C6"/>
@@ -4144,6 +4453,7 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B75:C75"/>
   </mergeCells>
